--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Oracle Fusion Workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21001236-CFBA-4787-9A95-1A4690E2404C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6C7259-3A03-43BF-86AB-913204BC06D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procurement" sheetId="1" r:id="rId1"/>
+    <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Item Description</t>
   </si>
@@ -58,6 +59,45 @@
   </si>
   <si>
     <t>Each</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>CRITICAL RIVER LOCATION</t>
+  </si>
+  <si>
+    <t>Ship to</t>
+  </si>
+  <si>
+    <t>Item in PO</t>
+  </si>
+  <si>
+    <t>CR1002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -127,11 +167,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,14 +523,68 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1">
-        <v>3</v>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1">
-        <v>30</v>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33F0F74-BC08-44D3-96F2-D90553CCF308}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,13 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6C7259-3A03-43BF-86AB-913204BC06D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195747F7-715C-426E-B7F1-6E9FCAD8A5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="6" activeTab="11" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
-    <sheet name="Procurement" sheetId="1" r:id="rId1"/>
-    <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId2"/>
+    <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
+    <sheet name="Procurement" sheetId="1" r:id="rId2"/>
+    <sheet name="Invoice With PO" sheetId="3" r:id="rId3"/>
+    <sheet name="Invoice Without PO" sheetId="5" r:id="rId4"/>
+    <sheet name="Batch Payment" sheetId="6" r:id="rId5"/>
+    <sheet name="Query Invoice" sheetId="7" r:id="rId6"/>
+    <sheet name="Account Receivables" sheetId="8" r:id="rId7"/>
+    <sheet name="AR Customer" sheetId="9" r:id="rId8"/>
+    <sheet name="BankStatement" sheetId="10" r:id="rId9"/>
+    <sheet name="BankStatement Reconciliation" sheetId="11" r:id="rId10"/>
+    <sheet name="Accounting Journal" sheetId="12" r:id="rId11"/>
+    <sheet name="Assets" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>Item Description</t>
   </si>
@@ -98,6 +108,93 @@
   </si>
   <si>
     <t>2026</t>
+  </si>
+  <si>
+    <t>Purchase Order</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Invoice Num</t>
+  </si>
+  <si>
+    <t>Payment Reason</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
+    <t>Supplier Expenses Payment</t>
+  </si>
+  <si>
+    <t>CR ELECTRONIC</t>
+  </si>
+  <si>
+    <t>Test_PO_17_1</t>
+  </si>
+  <si>
+    <t>CRPO500102</t>
+  </si>
+  <si>
+    <t>Test_WithoutPO_17_2</t>
+  </si>
+  <si>
+    <t>Batch Payment Val</t>
+  </si>
+  <si>
+    <t>MP_ELE_Payment_12</t>
+  </si>
+  <si>
+    <t>Test_Batch_06</t>
+  </si>
+  <si>
+    <t>Test_Inv_01</t>
+  </si>
+  <si>
+    <t>Receipt Num</t>
+  </si>
+  <si>
+    <t>Test_Receipt_01</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>CR_Test_001</t>
+  </si>
+  <si>
+    <t>Acc Desc</t>
+  </si>
+  <si>
+    <t>CR Test</t>
+  </si>
+  <si>
+    <t>Statement ID</t>
+  </si>
+  <si>
+    <t>Test_StatementID_017_01</t>
+  </si>
+  <si>
+    <t>Test_17_01</t>
+  </si>
+  <si>
+    <t>Journal name</t>
+  </si>
+  <si>
+    <t>Asset Number</t>
+  </si>
+  <si>
+    <t>Testing_Asset_001</t>
+  </si>
+  <si>
+    <t>Asset Key</t>
+  </si>
+  <si>
+    <t>0000</t>
   </si>
 </sst>
 </file>
@@ -488,6 +585,132 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33F0F74-BC08-44D3-96F2-D90553CCF308}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428B8DD4-9FCB-47DC-8CA2-12091BEC0F87}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F9F222-7252-4165-8712-A5E9128DF738}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3197F2C2-2421-4D3F-B4EF-60F377EE57B9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5A4D7D-D2F1-4871-9642-A9DEEF797E43}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -538,24 +761,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33F0F74-BC08-44D3-96F2-D90553CCF308}">
-  <dimension ref="A1:F2"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64E7892-C112-4B9E-A2C5-921B4D80ECD2}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>11</v>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>15</v>
@@ -566,16 +791,22 @@
       <c r="F1" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>18</v>
@@ -586,6 +817,163 @@
       <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66BFFF30-3000-4575-8F4F-87CE49820C18}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{701C3035-EF4B-48D0-ADB7-894FAC08DEC9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866FA2AA-CAE8-4919-B958-FC3781C83BF9}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045A02F2-5DFD-48B2-BD3C-EA1BA0943A05}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD69A5ED-56E7-4C95-8775-CD6654CE2286}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BBC424-D61B-41B1-B16D-CEC36E3C98E9}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195747F7-715C-426E-B7F1-6E9FCAD8A5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6F389A-F374-4B49-84E2-4AAECAB458BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="6" activeTab="11" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
@@ -158,9 +158,6 @@
     <t>Receipt Num</t>
   </si>
   <si>
-    <t>Test_Receipt_01</t>
-  </si>
-  <si>
     <t>Customer Name</t>
   </si>
   <si>
@@ -176,25 +173,28 @@
     <t>Statement ID</t>
   </si>
   <si>
-    <t>Test_StatementID_017_01</t>
-  </si>
-  <si>
-    <t>Test_17_01</t>
-  </si>
-  <si>
     <t>Journal name</t>
   </si>
   <si>
     <t>Asset Number</t>
   </si>
   <si>
-    <t>Testing_Asset_001</t>
-  </si>
-  <si>
     <t>Asset Key</t>
   </si>
   <si>
     <t>0000</t>
+  </si>
+  <si>
+    <t>Test_Receipt_06</t>
+  </si>
+  <si>
+    <t>Test_StatementID_017_07</t>
+  </si>
+  <si>
+    <t>Test_17_07</t>
+  </si>
+  <si>
+    <t>Testing_Asset_007</t>
   </si>
 </sst>
 </file>
@@ -648,12 +648,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -665,15 +665,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F9F222-7252-4165-8712-A5E9128DF738}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -691,18 +694,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -912,6 +915,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045A02F2-5DFD-48B2-BD3C-EA1BA0943A05}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
@@ -920,7 +926,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -938,18 +944,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -962,17 +968,17 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6F389A-F374-4B49-84E2-4AAECAB458BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577AFA41-0CBF-4260-AFD3-1402C7BDB748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="6" activeTab="11" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="4" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -185,9 +185,6 @@
     <t>0000</t>
   </si>
   <si>
-    <t>Test_Receipt_06</t>
-  </si>
-  <si>
     <t>Test_StatementID_017_07</t>
   </si>
   <si>
@@ -195,6 +192,9 @@
   </si>
   <si>
     <t>Testing_Asset_007</t>
+  </si>
+  <si>
+    <t>Test_Receipt_07</t>
   </si>
 </sst>
 </file>
@@ -653,7 +653,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -702,7 +702,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>45</v>
@@ -926,7 +926,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +978,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577AFA41-0CBF-4260-AFD3-1402C7BDB748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7D7643-0E14-4D84-B502-C0E17C886997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="4" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="6" activeTab="7" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Invoice Without PO" sheetId="5" r:id="rId4"/>
     <sheet name="Batch Payment" sheetId="6" r:id="rId5"/>
     <sheet name="Query Invoice" sheetId="7" r:id="rId6"/>
-    <sheet name="Account Receivables" sheetId="8" r:id="rId7"/>
-    <sheet name="AR Customer" sheetId="9" r:id="rId8"/>
+    <sheet name="AR Customer" sheetId="9" r:id="rId7"/>
+    <sheet name="Account Receivables" sheetId="8" r:id="rId8"/>
     <sheet name="BankStatement" sheetId="10" r:id="rId9"/>
     <sheet name="BankStatement Reconciliation" sheetId="11" r:id="rId10"/>
     <sheet name="Accounting Journal" sheetId="12" r:id="rId11"/>
@@ -194,7 +194,7 @@
     <t>Testing_Asset_007</t>
   </si>
   <si>
-    <t>Test_Receipt_07</t>
+    <t>Test_Receipt_08</t>
   </si>
 </sst>
 </file>
@@ -895,6 +895,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866FA2AA-CAE8-4919-B958-FC3781C83BF9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
@@ -912,6 +915,35 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD69A5ED-56E7-4C95-8775-CD6654CE2286}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045A02F2-5DFD-48B2-BD3C-EA1BA0943A05}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -927,35 +959,6 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD69A5ED-56E7-4C95-8775-CD6654CE2286}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7D7643-0E14-4D84-B502-C0E17C886997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676C9D26-E5AF-4055-B3F4-BD949AE8E47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="6" activeTab="7" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="1" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -134,36 +134,15 @@
     <t>CR ELECTRONIC</t>
   </si>
   <si>
-    <t>Test_PO_17_1</t>
-  </si>
-  <si>
-    <t>CRPO500102</t>
-  </si>
-  <si>
-    <t>Test_WithoutPO_17_2</t>
-  </si>
-  <si>
     <t>Batch Payment Val</t>
   </si>
   <si>
-    <t>MP_ELE_Payment_12</t>
-  </si>
-  <si>
-    <t>Test_Batch_06</t>
-  </si>
-  <si>
-    <t>Test_Inv_01</t>
-  </si>
-  <si>
     <t>Receipt Num</t>
   </si>
   <si>
     <t>Customer Name</t>
   </si>
   <si>
-    <t>CR_Test_001</t>
-  </si>
-  <si>
     <t>Acc Desc</t>
   </si>
   <si>
@@ -185,16 +164,37 @@
     <t>0000</t>
   </si>
   <si>
-    <t>Test_StatementID_017_07</t>
-  </si>
-  <si>
-    <t>Test_17_07</t>
-  </si>
-  <si>
-    <t>Testing_Asset_007</t>
-  </si>
-  <si>
-    <t>Test_Receipt_08</t>
+    <t>CR_Test_18_1</t>
+  </si>
+  <si>
+    <t>Test_StatementID_018_03</t>
+  </si>
+  <si>
+    <t>Test_18_03</t>
+  </si>
+  <si>
+    <t>Testing_Asset_18_03</t>
+  </si>
+  <si>
+    <t>Test_Receipt_18_2</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>CRPO500109</t>
+  </si>
+  <si>
+    <t>Test_PO_18_06</t>
+  </si>
+  <si>
+    <t>Test_WithoutPO_18_06</t>
+  </si>
+  <si>
+    <t>MP_ELE_Payment_18_4</t>
+  </si>
+  <si>
+    <t>Test_Batch_18_06</t>
   </si>
 </sst>
 </file>
@@ -648,12 +648,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -671,12 +671,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -689,23 +689,23 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -803,10 +803,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>23</v>
@@ -815,7 +815,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>20</v>
@@ -837,7 +837,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -850,7 +850,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>23</v>
@@ -875,15 +875,15 @@
         <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +896,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -906,7 +906,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -924,18 +924,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -948,17 +948,17 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -976,12 +976,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676C9D26-E5AF-4055-B3F4-BD949AE8E47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254319CB-0960-476B-AFEC-04676F39903A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="1" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" activeTab="4" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>Item Description</t>
   </si>
@@ -182,9 +182,6 @@
     <t>02</t>
   </si>
   <si>
-    <t>CRPO500109</t>
-  </si>
-  <si>
     <t>Test_PO_18_06</t>
   </si>
   <si>
@@ -195,6 +192,12 @@
   </si>
   <si>
     <t>Test_Batch_18_06</t>
+  </si>
+  <si>
+    <t>CRPO500110</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
 </sst>
 </file>
@@ -624,7 +627,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>19</v>
@@ -803,10 +806,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>23</v>
@@ -850,7 +853,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>23</v>
@@ -867,7 +870,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -880,10 +883,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -906,7 +909,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254319CB-0960-476B-AFEC-04676F39903A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A20C4D-012D-465C-BA53-273494A46EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" activeTab="4" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="1" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>Item Description</t>
   </si>
@@ -164,9 +164,6 @@
     <t>0000</t>
   </si>
   <si>
-    <t>CR_Test_18_1</t>
-  </si>
-  <si>
     <t>Test_StatementID_018_03</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t>Testing_Asset_18_03</t>
   </si>
   <si>
-    <t>Test_Receipt_18_2</t>
-  </si>
-  <si>
     <t>02</t>
   </si>
   <si>
@@ -198,6 +192,15 @@
   </si>
   <si>
     <t>14</t>
+  </si>
+  <si>
+    <t>Test_Receipt_18_3</t>
+  </si>
+  <si>
+    <t>CR_Test_18_2</t>
+  </si>
+  <si>
+    <t>CR_Test_18_3</t>
   </si>
 </sst>
 </file>
@@ -627,7 +630,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>19</v>
@@ -656,7 +659,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -679,7 +682,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +708,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>38</v>
@@ -806,10 +809,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>23</v>
@@ -818,7 +821,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>20</v>
@@ -853,7 +856,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>23</v>
@@ -883,10 +886,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +912,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +922,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD69A5ED-56E7-4C95-8775-CD6654CE2286}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -935,9 +938,17 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -961,7 +972,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +995,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A20C4D-012D-465C-BA53-273494A46EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E91754-C796-45DF-9B6C-802858A2A609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="1" activeTab="6" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" activeTab="1" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>Item Description</t>
   </si>
@@ -74,9 +74,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>CRITICAL RIVER LOCATION</t>
   </si>
   <si>
@@ -164,43 +161,55 @@
     <t>0000</t>
   </si>
   <si>
-    <t>Test_StatementID_018_03</t>
-  </si>
-  <si>
-    <t>Test_18_03</t>
-  </si>
-  <si>
-    <t>Testing_Asset_18_03</t>
-  </si>
-  <si>
     <t>02</t>
   </si>
   <si>
-    <t>Test_PO_18_06</t>
-  </si>
-  <si>
-    <t>Test_WithoutPO_18_06</t>
-  </si>
-  <si>
-    <t>MP_ELE_Payment_18_4</t>
-  </si>
-  <si>
-    <t>Test_Batch_18_06</t>
-  </si>
-  <si>
-    <t>CRPO500110</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Test_Receipt_18_3</t>
-  </si>
-  <si>
-    <t>CR_Test_18_2</t>
-  </si>
-  <si>
-    <t>CR_Test_18_3</t>
+    <t>Test_PO_19_01</t>
+  </si>
+  <si>
+    <t>Test_WithoutPO_19_01</t>
+  </si>
+  <si>
+    <t>Test_Batch_19_01</t>
+  </si>
+  <si>
+    <t>CR_Test_19_01</t>
+  </si>
+  <si>
+    <t>Test_Receipt_19_01</t>
+  </si>
+  <si>
+    <t>Test_StatementID_19_01</t>
+  </si>
+  <si>
+    <t>Test_19_01</t>
+  </si>
+  <si>
+    <t>Testing_Asset_19_01</t>
+  </si>
+  <si>
+    <t>MP_ELE_Payment_19_01</t>
+  </si>
+  <si>
+    <t>CRPO500111</t>
+  </si>
+  <si>
+    <t>CRPO500112</t>
+  </si>
+  <si>
+    <t>Test_PO_19_02</t>
+  </si>
+  <si>
+    <t>Test_PO_19_03</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
 </sst>
 </file>
@@ -601,42 +610,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -654,12 +663,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -677,12 +686,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -700,18 +709,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +771,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -772,65 +781,91 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64E7892-C112-4B9E-A2C5-921B4D80ECD2}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -848,18 +883,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -878,18 +913,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -907,12 +942,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +957,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD69A5ED-56E7-4C95-8775-CD6654CE2286}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -930,26 +965,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -967,12 +994,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -990,12 +1017,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
+++ b/Oracle_Tool_Automation/data/Oracle_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhaniKumarMaddi\git\OracleRepository\Oracle_Tool_Automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E91754-C796-45DF-9B6C-802858A2A609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83EDDA6-A694-496B-8BE0-E2074ABAC78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" activeTab="1" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="834" firstSheet="4" activeTab="8" xr2:uid="{7F354CF8-B21A-407D-B732-A31BC19C7C54}"/>
   </bookViews>
   <sheets>
     <sheet name="Procuremen_WithoutRequisition" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>Item Description</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Test_Receipt_19_01</t>
   </si>
   <si>
-    <t>Test_StatementID_19_01</t>
-  </si>
-  <si>
     <t>Test_19_01</t>
   </si>
   <si>
@@ -197,12 +194,6 @@
     <t>CRPO500112</t>
   </si>
   <si>
-    <t>Test_PO_19_02</t>
-  </si>
-  <si>
-    <t>Test_PO_19_03</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
@@ -210,6 +201,21 @@
   </si>
   <si>
     <t>40</t>
+  </si>
+  <si>
+    <t>Test_PO_19_04</t>
+  </si>
+  <si>
+    <t>Test_PO_19_05</t>
+  </si>
+  <si>
+    <t>Test_Receipt_19_02</t>
+  </si>
+  <si>
+    <t>Test_StatementID_19_03</t>
+  </si>
+  <si>
+    <t>Test_StatementID_19_04</t>
   </si>
 </sst>
 </file>
@@ -639,7 +645,7 @@
         <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>18</v>
@@ -668,7 +674,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +697,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +723,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>37</v>
@@ -771,7 +777,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -818,10 +824,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>22</v>
@@ -844,13 +850,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>17</v>
@@ -924,7 +930,7 @@
         <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -986,10 +992,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045A02F2-5DFD-48B2-BD3C-EA1BA0943A05}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1000,6 +1006,11 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1033,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
